--- a/sample-data/students.xlsx
+++ b/sample-data/students.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,147 +415,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>210001</v>
+        <v>ee220002001</v>
       </c>
       <c r="B2" t="str">
-        <v>Rahul Gupta</v>
+        <v>Test Student</v>
       </c>
       <c r="C2" t="str">
-        <v>rahul.gupta@iiti.ac.in</v>
+        <v>test.student@iiti.ac.in</v>
       </c>
       <c r="D2">
         <v>8.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>210002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Sneha Reddy</v>
-      </c>
-      <c r="C3" t="str">
-        <v>sneha.reddy@iiti.ac.in</v>
-      </c>
-      <c r="D3">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>210003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Arjun Nair</v>
-      </c>
-      <c r="C4" t="str">
-        <v>arjun.nair@iiti.ac.in</v>
-      </c>
-      <c r="D4">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>210004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Pooja Mishra</v>
-      </c>
-      <c r="C5" t="str">
-        <v>pooja.mishra@iiti.ac.in</v>
-      </c>
-      <c r="D5">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>210005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Karan Mehta</v>
-      </c>
-      <c r="C6" t="str">
-        <v>karan.mehta@iiti.ac.in</v>
-      </c>
-      <c r="D6">
-        <v>8.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>210006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Ananya Singh</v>
-      </c>
-      <c r="C7" t="str">
-        <v>ananya.singh@iiti.ac.in</v>
-      </c>
-      <c r="D7">
-        <v>9.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>210007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Rohan Joshi</v>
-      </c>
-      <c r="C8" t="str">
-        <v>rohan.joshi@iiti.ac.in</v>
-      </c>
-      <c r="D8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>210008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Divya Kapoor</v>
-      </c>
-      <c r="C9" t="str">
-        <v>divya.kapoor@iiti.ac.in</v>
-      </c>
-      <c r="D9">
-        <v>8.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>210009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Siddharth Rao</v>
-      </c>
-      <c r="C10" t="str">
-        <v>siddharth.rao@iiti.ac.in</v>
-      </c>
-      <c r="D10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>210010</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Meera Iyer</v>
-      </c>
-      <c r="C11" t="str">
-        <v>meera.iyer@iiti.ac.in</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>